--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487162_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487162_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5498</v>
+        <v>10.0071</v>
       </c>
       <c r="E2" t="n">
-        <v>9.053000000000001</v>
+        <v>7.7512</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4968</v>
+        <v>2.2559</v>
       </c>
       <c r="G2" t="n">
         <v>9.9955</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6268</v>
+        <v>2.0841</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8767</v>
+        <v>1.5748</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7502</v>
+        <v>0.5092</v>
       </c>
       <c r="V2" t="n">
         <v>0.2436</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.079700000000001</v>
+        <v>7.4867</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9873</v>
+        <v>5.8858</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0923</v>
+        <v>1.601</v>
       </c>
       <c r="G3" t="n">
         <v>6.0643</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8224</v>
+        <v>1.2294</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3875</v>
+        <v>1.286</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5652</v>
+        <v>-0.0565</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9841</v>
+        <v>6.8213</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1207</v>
+        <v>3.4226</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8634</v>
+        <v>3.3988</v>
       </c>
       <c r="G4" t="n">
         <v>4.3193</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9492</v>
+        <v>0.888</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5658</v>
+        <v>0.736</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3834</v>
+        <v>0.152</v>
       </c>
       <c r="V4" t="n">
         <v>1.228</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8272</v>
+        <v>3.8669</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5731</v>
+        <v>2.7734</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2541</v>
+        <v>1.0935</v>
       </c>
       <c r="G5" t="n">
         <v>4.9752</v>
@@ -844,13 +844,13 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6663</v>
+        <v>0.7059</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2512</v>
+        <v>0.4515</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4151</v>
+        <v>0.2545</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6562</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7421</v>
+        <v>1.6452</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3469</v>
+        <v>-1.3219</v>
       </c>
       <c r="F6" t="n">
-        <v>4.089</v>
+        <v>2.9671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2882</v>
+        <v>-0.2585</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7049</v>
+        <v>3.6979</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5833</v>
+        <v>-3.9564</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1473</v>
+        <v>-0.5195</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0659</v>
+        <v>4.0723</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0814</v>
+        <v>-4.5918</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1409</v>
+        <v>0.261</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.361</v>
+        <v>-0.3744</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5019</v>
+        <v>0.6355</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7021</v>
+        <v>0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8252</v>
+        <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1231</v>
+        <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4841</v>
+        <v>1.274</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0451</v>
+        <v>0.8841</v>
       </c>
       <c r="U6" t="n">
-        <v>2.439</v>
+        <v>0.3899</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3281</v>
+        <v>0.2436</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>0.2436</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.215</v>
+        <v>1.2616</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9281</v>
+        <v>1.0282</v>
       </c>
       <c r="F7" t="n">
-        <v>0.287</v>
+        <v>0.2334</v>
       </c>
       <c r="G7" t="n">
         <v>0.0174</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4257</v>
+        <v>0.4723</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3702</v>
+        <v>0.4703</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0555</v>
+        <v>0.002</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4227</v>
+        <v>0.8097</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2231</v>
+        <v>-2.0479</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6458</v>
+        <v>2.8576</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2585</v>
+        <v>1.2882</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6979</v>
+        <v>0.7049</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.9564</v>
+        <v>0.5833</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5195</v>
+        <v>1.1473</v>
       </c>
       <c r="K8" t="n">
-        <v>4.0723</v>
+        <v>1.0659</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.5918</v>
+        <v>0.0814</v>
       </c>
       <c r="M8" t="n">
-        <v>0.261</v>
+        <v>0.1409</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3744</v>
+        <v>-0.361</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6355</v>
+        <v>0.5019</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-4.8252</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0515</v>
+        <v>2.5517</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0172</v>
+        <v>1.3442</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0687</v>
+        <v>1.2076</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2436</v>
+        <v>-0.3281</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2436</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>E. VICENTE CARAZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1816</v>
+        <v>0.3905</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0181</v>
+        <v>0.1848</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1997</v>
+        <v>0.2057</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0385</v>
+        <v>0.4906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1014</v>
+        <v>0.3571</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.14</v>
+        <v>0.1335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0414</v>
+        <v>0.1035</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0414</v>
+        <v>0.1035</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0799</v>
+        <v>0.3871</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06</v>
+        <v>0.2536</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.14</v>
+        <v>0.1335</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2201</v>
+        <v>-0.0073</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0595</v>
+        <v>0.0813</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2796</v>
+        <v>-0.0886</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VICENTE CARAZO</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0155</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1729</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4906</v>
+        <v>-0.0385</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3571</v>
+        <v>0.1014</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1335</v>
+        <v>-0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1035</v>
+        <v>0.0414</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1035</v>
+        <v>0.0414</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3871</v>
+        <v>-0.0799</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2536</v>
+        <v>0.06</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1335</v>
+        <v>-0.14</v>
       </c>
       <c r="P10" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3146</v>
+        <v>0.2935</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.119</v>
+        <v>0.0407</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1957</v>
+        <v>0.2528</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0142</v>
+        <v>0.1127</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0414</v>
+        <v>0.1415</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0556</v>
+        <v>-0.0289</v>
       </c>
       <c r="G11" t="n">
         <v>0.1014</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1157</v>
+        <v>0.0112</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1157</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2228</v>
+        <v>-1.8084</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.582</v>
+        <v>-1.3817</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6409</v>
+        <v>-0.4267</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0786</v>
@@ -1390,13 +1390,13 @@
         <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0357</v>
+        <v>0.3787</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4587</v>
+        <v>0.659</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4944</v>
+        <v>-0.2803</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5295</v>
@@ -1426,10 +1426,10 @@
         <v>30.8483</v>
       </c>
       <c r="E13" t="n">
-        <v>16.518</v>
+        <v>16.5181</v>
       </c>
       <c r="F13" t="n">
-        <v>14.3302</v>
+        <v>14.3303</v>
       </c>
       <c r="G13" t="n">
         <v>25.8763</v>
@@ -1438,7 +1438,7 @@
         <v>27.308</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4316</v>
+        <v>-1.431599999999999</v>
       </c>
       <c r="J13" t="n">
         <v>24.7377</v>
@@ -1468,16 +1468,16 @@
         <v>13.5106</v>
       </c>
       <c r="S13" t="n">
-        <v>9.881699999999999</v>
+        <v>9.881500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>7.627900000000001</v>
+        <v>7.628000000000001</v>
       </c>
       <c r="U13" t="n">
         <v>2.2537</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.08449999999999996</v>
+        <v>-0.08449999999999991</v>
       </c>
       <c r="W13" t="n">
         <v>2.4884</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2772</v>
+        <v>3.8892</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5643</v>
+        <v>3.364</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7129</v>
+        <v>0.5252</v>
       </c>
       <c r="G14" t="n">
         <v>4.1648</v>
@@ -1546,13 +1546,13 @@
         <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3054</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.234</v>
+        <v>0.0338</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0713</v>
+        <v>-0.1164</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0131</v>
+        <v>0.2669</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3287</v>
+        <v>2.529</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3156</v>
+        <v>-2.262</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9893</v>
@@ -1624,13 +1624,13 @@
         <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8421</v>
+        <v>-0.5883</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3741</v>
+        <v>-0.1738</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.468</v>
+        <v>-0.4145</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8576</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>A. DEL VAL IBAÑEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.808</v>
+        <v>-2.4868</v>
       </c>
       <c r="E16" t="n">
-        <v>1.125</v>
+        <v>-0.4921</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.9331</v>
+        <v>-1.9947</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.1127</v>
+        <v>-2.0434</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7985</v>
+        <v>-0.0341</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3142</v>
+        <v>-2.0092</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8663</v>
+        <v>-0.9885</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.0143</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1057</v>
+        <v>-2.0028</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.979</v>
+        <v>-1.0548</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.5591</v>
+        <v>-1.0484</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4199</v>
+        <v>-0.0064</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8534</v>
+        <v>-0.7872</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6411</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2123</v>
+        <v>-0.7119</v>
       </c>
       <c r="V16" t="n">
-        <v>0.614</v>
+        <v>-0.0422</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8999</v>
+        <v>0.5717</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2859</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>R. HERNANSANZ HERRERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.933</v>
+        <v>-2.5966</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3672</v>
+        <v>-2.3089</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5658</v>
+        <v>-0.2877</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5419</v>
+        <v>-1.7836</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.744</v>
+        <v>-2.132</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2021</v>
+        <v>0.3484</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0605</v>
+        <v>-1.1089</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6467000000000001</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>-0.5862000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6024</v>
+        <v>-0.6747</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3906</v>
+        <v>-1.6093</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7883</v>
+        <v>0.9346</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>-0.386</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7192</v>
+        <v>-0.427</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4627</v>
+        <v>-0.235</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2566</v>
+        <v>-0.192</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DEL VAL IBAÑEZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9409</v>
+        <v>-2.6392</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8927</v>
+        <v>-1.3672</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0482</v>
+        <v>-1.272</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0434</v>
+        <v>-1.5419</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0341</v>
+        <v>-1.744</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0092</v>
+        <v>0.2021</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9885</v>
+        <v>0.0605</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0143</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0028</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0548</v>
+        <v>-1.6024</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0484</v>
+        <v>-2.3906</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0064</v>
+        <v>0.7883</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2413</v>
+        <v>-1.4254</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4759</v>
+        <v>-0.4627</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7654</v>
+        <v>-0.9628</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0422</v>
+        <v>0.3281</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.614</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. HERNANSANZ HERRERO</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0573</v>
+        <v>-2.6814</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6093</v>
+        <v>1.2252</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.448</v>
+        <v>-3.9066</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7836</v>
+        <v>-3.1127</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.132</v>
+        <v>-2.7985</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3484</v>
+        <v>-0.3142</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1089</v>
+        <v>0.8663</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.1057</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6747</v>
+        <v>-3.979</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6093</v>
+        <v>-3.5591</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9346</v>
+        <v>-0.4199</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8877</v>
+        <v>-1.7268</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5354</v>
+        <v>-0.541</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3523</v>
+        <v>-1.1858</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1498</v>
+        <v>-4.8643</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9214</v>
+        <v>-3.8227</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2284</v>
+        <v>-1.0416</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6962</v>
@@ -2014,13 +2014,13 @@
         <v>3.0881</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3377</v>
+        <v>-1.0523</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7959000000000001</v>
+        <v>-0.1054</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1336</v>
+        <v>-0.9469</v>
       </c>
       <c r="V20" t="n">
         <v>0.6562</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0417</v>
+        <v>-6.0794</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9544</v>
+        <v>-4.9131</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0873</v>
+        <v>-1.1662</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.1322</v>
+        <v>-6.6865</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.1843</v>
+        <v>-4.1089</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0521</v>
+        <v>-2.5776</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1695</v>
+        <v>-3.455</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.2345</v>
+        <v>-0.8903</v>
       </c>
       <c r="L21" t="n">
-        <v>0.065</v>
+        <v>-2.5647</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9627</v>
+        <v>-3.2315</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9498</v>
+        <v>-3.2186</v>
       </c>
       <c r="O21" t="n">
         <v>-0.0129</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>1.5441</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.158</v>
+        <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1025</v>
+        <v>-0.9369</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1057</v>
+        <v>-0.4931</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9968</v>
+        <v>-0.4439</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DE LARREA ASENJO</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5671</v>
+        <v>-6.1015</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.69</v>
+        <v>-4.2549</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8771</v>
+        <v>-1.8467</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.0555</v>
+        <v>-5.1322</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.4464</v>
+        <v>-5.1843</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6091</v>
+        <v>0.0521</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.171</v>
+        <v>-3.1695</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-3.2345</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2702</v>
+        <v>0.065</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8845</v>
+        <v>-1.9627</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.5457</v>
+        <v>-1.9498</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6612</v>
+        <v>-0.0129</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.193</v>
+        <v>0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7046</v>
+        <v>-1.1623</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1956</v>
+        <v>-0.4062</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.509</v>
+        <v>-0.7562</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5717</v>
+        <v>0.2859</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1857</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>M. DE LARREA ASENJO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6409</v>
+        <v>-6.2201</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9131</v>
+        <v>-4.2894</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7277</v>
+        <v>-1.9307</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.6865</v>
+        <v>-5.0555</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.1089</v>
+        <v>-4.4464</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5776</v>
+        <v>-0.6091</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.455</v>
+        <v>-2.171</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8903</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5647</v>
+        <v>-1.2702</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.2315</v>
+        <v>-2.8845</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.2186</v>
+        <v>-3.5457</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0129</v>
+        <v>0.6612</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5441</v>
+        <v>-0.193</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5091</v>
+        <v>2.7021</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4984</v>
+        <v>-0.3576</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4931</v>
+        <v>0.2049</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0054</v>
+        <v>-0.5625</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-30.84840000000001</v>
+        <v>-29.5132</v>
       </c>
       <c r="E24" t="n">
         <v>-14.3301</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.5183</v>
+        <v>-15.183</v>
       </c>
       <c r="G24" t="n">
         <v>-25.8765</v>
@@ -2296,13 +2296,13 @@
         <v>-27.308</v>
       </c>
       <c r="I24" t="n">
-        <v>1.431600000000001</v>
+        <v>1.4316</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.138699999999999</v>
+        <v>-1.1387</v>
       </c>
       <c r="K24" t="n">
-        <v>1.338700000000002</v>
+        <v>1.3387</v>
       </c>
       <c r="L24" t="n">
         <v>-2.477400000000001</v>
@@ -2326,16 +2326,16 @@
         <v>18.3356</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.881499999999999</v>
+        <v>-8.546399999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.2537</v>
+        <v>-2.2538</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.6281</v>
+        <v>-6.292899999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>0.08449999999999991</v>
+        <v>0.08450000000000002</v>
       </c>
       <c r="W24" t="n">
         <v>2.5728</v>
